--- a/results/2019_occ_all.xlsx
+++ b/results/2019_occ_all.xlsx
@@ -583,13 +583,13 @@
         <v>0.362</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.636</v>
+        <v>0.646</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.739</v>
+        <v>0.745</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261</v>
+        <v>0.255</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0.064</v>
@@ -598,10 +598,10 @@
         <v>0.181</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.258</v>
+        <v>0.259</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.44</v>
+        <v>0.444</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>occ_deep_svd</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1036,29 +1036,29 @@
       <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0.667</v>
+      <c r="D8" s="5" t="n">
+        <v>0.444</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0.667</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.511</v>
+        <v>0.859</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.477</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.631</v>
+        <v>0.656</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
@@ -1078,7 +1078,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>occ_deep_svd</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1089,29 +1089,29 @@
       <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>0.444</v>
+      <c r="D9" s="6" t="n">
+        <v>0.667</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>0.667</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>0.667</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.472</v>
+        <v>0.802</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.511</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.602</v>
+        <v>0.631</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>0</v>
@@ -6993,10 +6993,10 @@
       <c r="E84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="6" t="n">
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="n">
         <v>0.44</v>
       </c>
       <c r="H84" s="5" t="n">
@@ -7005,13 +7005,13 @@
       <c r="I84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="6" t="n">
+      <c r="J84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="L84" s="6" t="n">
+      <c r="L84" s="5" t="n">
         <v>0.061</v>
       </c>
       <c r="M84" s="6" t="n">
@@ -7055,25 +7055,25 @@
         <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.347</v>
+        <v>0.5</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>0.622</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.653</v>
+        <v>0.378</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>0.026</v>
+        <v>0.001</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>0.188</v>
       </c>
       <c r="M85" s="6" t="n">
         <v>0</v>
